--- a/data/Простой.xlsx
+++ b/data/Простой.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>13.02.2026 0:00:00</t>
+          <t>13.02.2025 0:00:00</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>13.02.2026 0:00:00</t>
+          <t>13.02.2025 0:00:00</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>13.01.2026 0:00:00</t>
+          <t>13.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>13.01.2026 0:00:00</t>
+          <t>13.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>23.02.2026 0:00:00</t>
+          <t>23.02.2025 0:00:00</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>23.02.2026 0:00:00</t>
+          <t>23.02.2025 0:00:00</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>26.01.2026 0:00:00</t>
+          <t>26.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>26.01.2026 0:00:00</t>
+          <t>26.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>02.02.2026 0:00:00</t>
+          <t>02.02.2025 0:00:00</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>02.02.2026 0:00:00</t>
+          <t>02.02.2025 0:00:00</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>15.01.2026 0:00:00</t>
+          <t>15.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>15.01.2026 0:00:00</t>
+          <t>15.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>25.01.2026 0:00:00</t>
+          <t>25.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>25.01.2026 0:00:00</t>
+          <t>25.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>21.01.2026 0:00:00</t>
+          <t>21.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>21.01.2026 0:00:00</t>
+          <t>21.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>24.01.2026 0:00:00</t>
+          <t>24.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>24.01.2026 0:00:00</t>
+          <t>24.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>04.01.2026 0:00:00</t>
+          <t>04.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>04.01.2026 0:00:00</t>
+          <t>04.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>06.01.2026 0:00:00</t>
+          <t>06.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>06.01.2026 0:00:00</t>
+          <t>06.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>10.01.2026 0:00:00</t>
+          <t>10.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>10.01.2026 0:00:00</t>
+          <t>10.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>01.03.2026 0:00:00</t>
+          <t>01.03.2025 0:00:00</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>01.03.2026 0:00:00</t>
+          <t>01.03.2025 0:00:00</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>15.01.2026 0:00:00</t>
+          <t>15.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
@@ -6763,7 +6763,7 @@
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>15.01.2026 0:00:00</t>
+          <t>15.01.2025 0:00:00</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
